--- a/etf_holdings/2026-10-20_00981A_full_holdings.xlsx
+++ b/etf_holdings/2026-10-20_00981A_full_holdings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M51"/>
+  <dimension ref="A1:M52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-20 00:27:57</t>
+          <t>2026-10-20 21:40:53</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -509,35 +509,33 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>-0.62%2405</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>-0.62%</t>
+        </is>
+      </c>
+      <c r="H2" t="n">
+        <v>2405</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>10.86%12,392,000</t>
+          <t>11.30%12,671,000</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>10.86%</t>
+          <t>11.30%</t>
         </is>
       </c>
       <c r="K2" t="n">
-        <v>12392000</v>
+        <v>12671000</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-0.07%</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -554,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-20 00:27:57</t>
+          <t>2026-10-20 21:40:53</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -572,27 +570,25 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>-3.51%4945</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>-3.51%</t>
+        </is>
+      </c>
+      <c r="H3" t="n">
+        <v>4945</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>8.04%4,328,000</t>
+          <t>7.93%4,328,000</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>8.04%</t>
+          <t>7.93%</t>
         </is>
       </c>
       <c r="K3" t="n">
@@ -600,7 +596,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-0.28%</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -617,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-20 00:27:57</t>
+          <t>2026-10-20 21:40:53</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -630,27 +626,25 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>3037欣興</t>
+          <t>2454聯發科</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>-1.31%4150</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>-1.31%</t>
+        </is>
+      </c>
+      <c r="H4" t="n">
+        <v>4150</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>7.91%19,499,000</t>
+          <t>7.91%5,143,000</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -659,11 +653,11 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>19499000</v>
+        <v>5143000</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-0.10%</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -680,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-20 00:27:57</t>
+          <t>2026-10-20 21:40:53</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -693,40 +687,38 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2454聯發科</t>
+          <t>3017奇鋐</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>+0.15%3325</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>+0.15%</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
+        <v>3325</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>7.84%5,143,000</t>
+          <t>7.82%6,343,000</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>7.84%</t>
+          <t>7.82%</t>
         </is>
       </c>
       <c r="K5" t="n">
-        <v>5143000</v>
+        <v>6343000</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -743,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-20 00:27:57</t>
+          <t>2026-10-20 21:40:53</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -756,40 +748,38 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>3017奇鋐</t>
+          <t>3037欣興</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>-5.8%1055</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>-5.8%</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
+        <v>1055</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>7.58%6,303,000</t>
+          <t>7.63%19,499,000</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>7.58%</t>
+          <t>7.63%</t>
         </is>
       </c>
       <c r="K6" t="n">
-        <v>6303000</v>
+        <v>19499000</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-0.46%</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -806,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-20 00:27:57</t>
+          <t>2026-10-20 21:40:53</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -824,35 +814,33 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>+1.37%6650</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>+1.37%</t>
+        </is>
+      </c>
+      <c r="H7" t="n">
+        <v>6650</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>5.95%2,502,000</t>
+          <t>6.19%2,512,000</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>5.95%</t>
+          <t>6.19%</t>
         </is>
       </c>
       <c r="K7" t="n">
-        <v>2502000</v>
+        <v>2512000</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>+0.08%</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -869,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-20 00:27:57</t>
+          <t>2026-10-20 21:40:53</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -882,40 +870,38 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>6223旺矽</t>
+          <t>2345智邦</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>-1.75%1970</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>-1.75%</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
+        <v>1970</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>4.75%2,504,000</t>
+          <t>4.57%6,264,000</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>4.75%</t>
+          <t>4.57%</t>
         </is>
       </c>
       <c r="K8" t="n">
-        <v>2504000</v>
+        <v>6264000</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-0.08%</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -932,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-20 00:27:57</t>
+          <t>2026-10-20 21:40:53</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -950,27 +936,25 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>-2.06%523</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>-2.06%</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
+        <v>523</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>4.55%23,519,000</t>
+          <t>4.56%23,519,000</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>4.55%</t>
+          <t>4.56%</t>
         </is>
       </c>
       <c r="K9" t="n">
@@ -978,7 +962,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-0.09%</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -995,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-20 00:27:57</t>
+          <t>2026-10-20 21:40:53</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1008,27 +992,25 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2345智邦</t>
+          <t>6223旺矽</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>-6.4%4900</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>-6.4%</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
+        <v>4900</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>4.55%6,264,000</t>
+          <t>4.55%2,504,000</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1037,11 +1019,11 @@
         </is>
       </c>
       <c r="K10" t="n">
-        <v>6264000</v>
+        <v>2504000</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-0.31%</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1058,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-20 00:27:57</t>
+          <t>2026-10-20 21:40:53</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1076,27 +1058,25 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>-2.13%1605</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>-2.13%</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
+        <v>1605</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>4.50%7,582,000</t>
+          <t>4.51%7,582,000</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>4.50%</t>
+          <t>4.51%</t>
         </is>
       </c>
       <c r="K11" t="n">
@@ -1104,7 +1084,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-0.10%</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1121,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-20 00:27:57</t>
+          <t>2026-10-20 21:40:53</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1139,27 +1119,25 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>-5.43%1305</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>-5.43%</t>
+        </is>
+      </c>
+      <c r="H12" t="n">
+        <v>1305</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>4.47%8,937,000</t>
+          <t>4.32%8,937,000</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>4.47%</t>
+          <t>4.32%</t>
         </is>
       </c>
       <c r="K12" t="n">
@@ -1167,7 +1145,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-0.24%</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1184,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-20 00:27:57</t>
+          <t>2026-10-20 21:40:53</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1202,27 +1180,25 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>-4.91%1550</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>-4.91%</t>
+        </is>
+      </c>
+      <c r="H13" t="n">
+        <v>1550</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>4.27%7,224,000</t>
+          <t>4.15%7,224,000</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>4.27%</t>
+          <t>4.15%</t>
         </is>
       </c>
       <c r="K13" t="n">
@@ -1230,7 +1206,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-0.21%</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1247,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-20 00:27:57</t>
+          <t>2026-10-20 21:40:53</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1265,27 +1241,25 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>-3.42%127</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>-3.42%</t>
+        </is>
+      </c>
+      <c r="H14" t="n">
+        <v>127</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>3.79%79,618,000</t>
+          <t>3.75%79,618,000</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>3.79%</t>
+          <t>3.75%</t>
         </is>
       </c>
       <c r="K14" t="n">
@@ -1293,7 +1267,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-0.13%</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1310,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-20 00:27:57</t>
+          <t>2026-10-20 21:40:53</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1328,27 +1302,25 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>-5.2%1185</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>-5.2%</t>
+        </is>
+      </c>
+      <c r="H15" t="n">
+        <v>1185</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>3.12%6,899,000</t>
+          <t>3.03%6,899,000</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>3.12%</t>
+          <t>3.03%</t>
         </is>
       </c>
       <c r="K15" t="n">
@@ -1356,7 +1328,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-0.16%</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1373,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-20 00:27:57</t>
+          <t>2026-10-20 21:40:53</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1391,27 +1363,25 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>-1.09%7745</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>-1.09%</t>
+        </is>
+      </c>
+      <c r="H16" t="n">
+        <v>7745</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2.42%852,000</t>
+          <t>2.45%852,000</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2.42%</t>
+          <t>2.45%</t>
         </is>
       </c>
       <c r="K16" t="n">
@@ -1419,7 +1389,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1436,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-10-20 00:28:02</t>
+          <t>2026-10-20 21:40:55</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1454,27 +1424,27 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>+2.17%1885</t>
+          <t>+2.12%1925</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>+2.17%</t>
+          <t>+2.12%</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>1885</t>
+          <t>1925</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2.24%3,281,561</t>
+          <t>2.34%3,281,561</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2.24%</t>
+          <t>2.34%</t>
         </is>
       </c>
       <c r="K17" t="n">
@@ -1499,7 +1469,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-10-20 00:28:02</t>
+          <t>2026-10-20 21:40:55</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1517,27 +1487,27 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>-1.99%1975</t>
+          <t>-2.53%1925</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-1.99%</t>
+          <t>-2.53%</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>1975</t>
+          <t>1925</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>2.07%2,887,848</t>
+          <t>2.06%2,887,848</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>2.07%</t>
+          <t>2.06%</t>
         </is>
       </c>
       <c r="K18" t="n">
@@ -1545,7 +1515,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>-0.04%</t>
+          <t>-0.05%</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -1562,7 +1532,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-10-20 00:28:02</t>
+          <t>2026-10-20 21:40:55</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1580,27 +1550,27 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>-0.15%670</t>
+          <t>-1.49%660</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-0.15%</t>
+          <t>-1.49%</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>670</t>
+          <t>660</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>2.03%8,348,000</t>
+          <t>2.04%8,348,000</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>2.03%</t>
+          <t>2.04%</t>
         </is>
       </c>
       <c r="K19" t="n">
@@ -1608,7 +1578,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1625,7 +1595,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-10-20 00:28:02</t>
+          <t>2026-10-20 21:40:55</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1643,27 +1613,27 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>-3.03%15980</t>
+          <t>-0.5%15900</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-3.03%</t>
+          <t>-0.5%</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>15980</t>
+          <t>15900</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1.17%201,900</t>
+          <t>1.19%201,900</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>1.17%</t>
+          <t>1.19%</t>
         </is>
       </c>
       <c r="K20" t="n">
@@ -1671,7 +1641,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>-0.04%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -1688,7 +1658,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-10-20 00:28:02</t>
+          <t>2026-10-20 21:40:55</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1706,35 +1676,35 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>+3.78%2335</t>
+          <t>-1.93%2290</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>+3.78%</t>
+          <t>-1.93%</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2335</t>
+          <t>2290</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>0.65%769,000</t>
+          <t>0.70%819,000</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>0.65%</t>
+          <t>0.70%</t>
         </is>
       </c>
       <c r="K21" t="n">
-        <v>769000</v>
+        <v>819000</v>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -1751,7 +1721,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-10-20 00:28:02</t>
+          <t>2026-10-20 21:40:55</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1764,40 +1734,40 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>8996高力</t>
+          <t>2449京元電子</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>-2.87%1525</t>
+          <t>-1.52%259.5</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-2.87%</t>
+          <t>-1.52%</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>1525</t>
+          <t>259.5</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>0.54%981,000</t>
+          <t>0.61%6,351,450</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>0.54%</t>
+          <t>0.61%</t>
         </is>
       </c>
       <c r="K22" t="n">
-        <v>981000</v>
+        <v>6351450</v>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -1814,7 +1784,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-10-20 00:28:02</t>
+          <t>2026-10-20 21:40:55</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1827,36 +1797,36 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>6510精測</t>
+          <t>8996高力</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>+1.76%3175</t>
+          <t>+1.31%1545</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>+1.76%</t>
+          <t>+1.31%</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>3175</t>
+          <t>1545</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>0.54%470,000</t>
+          <t>0.56%981,000</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>0.54%</t>
+          <t>0.56%</t>
         </is>
       </c>
       <c r="K23" t="n">
-        <v>470000</v>
+        <v>981000</v>
       </c>
       <c r="L23" t="inlineStr">
         <is>
@@ -1877,7 +1847,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-10-20 00:28:02</t>
+          <t>2026-10-20 21:40:55</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1890,40 +1860,40 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2449京元電子</t>
+          <t>6510精測</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>-4.18%263.5</t>
+          <t>-2.52%3095</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>-4.18%</t>
+          <t>-2.52%</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>263.5</t>
+          <t>3095</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>0.49%5,151,450</t>
+          <t>0.54%470,000</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>0.49%</t>
+          <t>0.54%</t>
         </is>
       </c>
       <c r="K24" t="n">
-        <v>5151450</v>
+        <v>470000</v>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -1940,7 +1910,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-10-20 00:28:02</t>
+          <t>2026-10-20 21:40:55</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1953,40 +1923,40 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>3264欣銓</t>
+          <t>3231緯創</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>-0.19%258</t>
+          <t>+5%189</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>-0.19%</t>
+          <t>+5%</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>258</t>
+          <t>189</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>0.25%2,657,000</t>
+          <t>0.33%4,703,000</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>0.25%</t>
+          <t>0.33%</t>
         </is>
       </c>
       <c r="K25" t="n">
-        <v>2657000</v>
+        <v>4703000</v>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -2003,7 +1973,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-10-20 00:28:02</t>
+          <t>2026-10-20 21:40:55</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,40 +1986,40 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>6271同欣電</t>
+          <t>3264欣銓</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>-1.53%225.5</t>
+          <t>-4.26%247</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>-1.53%</t>
+          <t>-4.26%</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>225.5</t>
+          <t>247</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>0.18%2,185,000</t>
+          <t>0.24%2,657,000</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>0.18%</t>
+          <t>0.24%</t>
         </is>
       </c>
       <c r="K26" t="n">
-        <v>2185000</v>
+        <v>2657000</v>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2066,7 +2036,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-10-20 00:28:02</t>
+          <t>2026-10-20 21:40:55</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2079,36 +2049,36 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>4979華星光</t>
+          <t>6271同欣電</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>-7.69%480</t>
+          <t>-2.88%219</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>-7.69%</t>
+          <t>-2.88%</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>480</t>
+          <t>219</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>0.17%957,000</t>
+          <t>0.18%2,185,000</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>0.17%</t>
+          <t>0.18%</t>
         </is>
       </c>
       <c r="K27" t="n">
-        <v>957000</v>
+        <v>2185000</v>
       </c>
       <c r="L27" t="inlineStr">
         <is>
@@ -2129,7 +2099,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-10-20 00:28:02</t>
+          <t>2026-10-20 21:40:55</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2142,27 +2112,27 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>6515穎崴</t>
+          <t>4979華星光</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>0%5160</t>
+          <t>-2.08%470</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-2.08%</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>5160</t>
+          <t>470</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>0.17%93,000</t>
+          <t>0.17%957,000</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -2171,11 +2141,11 @@
         </is>
       </c>
       <c r="K28" t="n">
-        <v>93000</v>
+        <v>957000</v>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -2192,7 +2162,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-10-20 00:28:02</t>
+          <t>2026-10-20 21:40:55</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2205,40 +2175,40 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>8210勤誠</t>
+          <t>6515穎崴</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>-2.52%813</t>
+          <t>-3.88%4960</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>-2.52%</t>
+          <t>-3.88%</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>813</t>
+          <t>4960</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>0.14%478,000</t>
+          <t>0.17%93,000</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>0.14%</t>
+          <t>0.17%</t>
         </is>
       </c>
       <c r="K29" t="n">
-        <v>478000</v>
+        <v>93000</v>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -2255,7 +2225,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-10-20 00:28:02</t>
+          <t>2026-10-20 21:40:55</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2268,36 +2238,36 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>6191精成科</t>
+          <t>8210勤誠</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>-1.41%91</t>
+          <t>-1.48%801</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>-1.41%</t>
+          <t>-1.48%</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>801</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>0.13%3,921,000</t>
+          <t>0.14%478,000</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>0.13%</t>
+          <t>0.14%</t>
         </is>
       </c>
       <c r="K30" t="n">
-        <v>3921000</v>
+        <v>478000</v>
       </c>
       <c r="L30" t="inlineStr">
         <is>
@@ -2318,7 +2288,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-10-20 00:28:03</t>
+          <t>2026-10-20 21:40:56</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2331,38 +2301,38 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>8358金居</t>
+          <t>6191精成科</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>+2.54%484</t>
+          <t>-0.55%90.5</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>+2.54%</t>
+          <t>-0.55%</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>484</v>
+        <v>90.5</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>0.11%654,000</t>
+          <t>0.13%3,921,000</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>0.11%</t>
+          <t>0.13%</t>
         </is>
       </c>
       <c r="K31" t="n">
-        <v>654000</v>
+        <v>3921000</v>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -2379,7 +2349,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-10-20 00:28:03</t>
+          <t>2026-10-20 21:40:56</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2397,25 +2367,25 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>-1.7%173</t>
+          <t>+3.18%178.5</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>-1.7%</t>
+          <t>+3.18%</t>
         </is>
       </c>
       <c r="H32" t="n">
-        <v>173</v>
+        <v>178.5</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>0.11%1,740,000</t>
+          <t>0.12%1,740,000</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>0.11%</t>
+          <t>0.12%</t>
         </is>
       </c>
       <c r="K32" t="n">
@@ -2423,7 +2393,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -2440,7 +2410,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-10-20 00:28:03</t>
+          <t>2026-10-20 21:40:56</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2453,34 +2423,34 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>6187萬潤</t>
+          <t>8358金居</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>-0.35%1405</t>
+          <t>-3%469.5</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>-0.35%</t>
+          <t>-3%</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>1405</v>
+        <v>469.5</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>0.06%121,000</t>
+          <t>0.11%654,000</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>0.06%</t>
+          <t>0.11%</t>
         </is>
       </c>
       <c r="K33" t="n">
-        <v>121000</v>
+        <v>654000</v>
       </c>
       <c r="L33" t="inlineStr">
         <is>
@@ -2501,7 +2471,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-10-20 00:28:03</t>
+          <t>2026-10-20 21:40:56</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2514,38 +2484,38 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2313華通</t>
+          <t>6187萬潤</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>0%248</t>
+          <t>-6.05%1320</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-6.05%</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>248</v>
+        <v>1320</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>0.05%501,000</t>
+          <t>0.06%121,000</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>0.05%</t>
+          <t>0.06%</t>
         </is>
       </c>
       <c r="K34" t="n">
-        <v>501000</v>
+        <v>121000</v>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -2562,7 +2532,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-10-20 00:28:03</t>
+          <t>2026-10-20 21:40:56</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2575,34 +2545,34 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2002中鋼</t>
+          <t>2313華通</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>-0.26%19.5</t>
+          <t>-1.81%243.5</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>-0.26%</t>
+          <t>-1.81%</t>
         </is>
       </c>
       <c r="H35" t="n">
-        <v>19.5</v>
+        <v>243.5</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>0.04%5,163,000</t>
+          <t>0.05%501,000</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>0.04%</t>
+          <t>0.05%</t>
         </is>
       </c>
       <c r="K35" t="n">
-        <v>5163000</v>
+        <v>501000</v>
       </c>
       <c r="L35" t="inlineStr">
         <is>
@@ -2623,7 +2593,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-10-20 00:28:03</t>
+          <t>2026-10-20 21:40:56</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2636,34 +2606,34 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>6278台表科</t>
+          <t>2002中鋼</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>-3.02%289.5</t>
+          <t>+0.51%19.6</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>-3.02%</t>
+          <t>+0.51%</t>
         </is>
       </c>
       <c r="H36" t="n">
-        <v>289.5</v>
+        <v>19.6</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>0%1,000</t>
+          <t>0.04%5,163,000</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.04%</t>
         </is>
       </c>
       <c r="K36" t="n">
-        <v>1000</v>
+        <v>5163000</v>
       </c>
       <c r="L36" t="inlineStr">
         <is>
@@ -2684,7 +2654,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-10-20 00:28:03</t>
+          <t>2026-10-20 21:40:56</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2697,21 +2667,21 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>3661世芯-KY</t>
+          <t>6278台表科</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>+0.81%3715</t>
+          <t>-0.52%288</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>+0.81%</t>
+          <t>-0.52%</t>
         </is>
       </c>
       <c r="H37" t="n">
-        <v>3715</v>
+        <v>288</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
@@ -2745,7 +2715,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-10-20 00:28:03</t>
+          <t>2026-10-20 21:40:56</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2758,21 +2728,21 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2439美律</t>
+          <t>3661世芯-KY</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>-2.7%79.3</t>
+          <t>-2.02%3640</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>-2.7%</t>
+          <t>-2.02%</t>
         </is>
       </c>
       <c r="H38" t="n">
-        <v>79.3</v>
+        <v>3640</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
@@ -2806,7 +2776,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-10-20 00:28:03</t>
+          <t>2026-10-20 21:40:56</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2819,21 +2789,21 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>1590亞德客-KY</t>
+          <t>2439美律</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>+0.87%1165</t>
+          <t>+0.38%79.6</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>+0.87%</t>
+          <t>+0.38%</t>
         </is>
       </c>
       <c r="H39" t="n">
-        <v>1165</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
@@ -2867,7 +2837,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-10-20 00:28:03</t>
+          <t>2026-10-20 21:40:56</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2880,21 +2850,21 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>3008大立光</t>
+          <t>1590亞德客-KY</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>-2.42%6245</t>
+          <t>-4.72%1110</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>-2.42%</t>
+          <t>-4.72%</t>
         </is>
       </c>
       <c r="H40" t="n">
-        <v>6245</v>
+        <v>1110</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
@@ -2928,7 +2898,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-10-20 00:28:03</t>
+          <t>2026-10-20 21:40:56</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2941,21 +2911,21 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>4958臻鼎-KY</t>
+          <t>3008大立光</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>-1.8%547</t>
+          <t>-4.32%5975</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>-1.8%</t>
+          <t>-4.32%</t>
         </is>
       </c>
       <c r="H41" t="n">
-        <v>547</v>
+        <v>5975</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
@@ -2989,7 +2959,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-10-20 00:28:03</t>
+          <t>2026-10-20 21:40:56</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -3002,21 +2972,21 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>2382廣達</t>
+          <t>4958臻鼎-KY</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>-2.33%314.5</t>
+          <t>0%547</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>-2.33%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="H42" t="n">
-        <v>314.5</v>
+        <v>547</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
@@ -3050,7 +3020,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-10-20 00:28:03</t>
+          <t>2026-10-20 21:40:56</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3063,21 +3033,21 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>2408南亞科</t>
+          <t>2382廣達</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>-2.57%436</t>
+          <t>+1.91%320.5</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>-2.57%</t>
+          <t>+1.91%</t>
         </is>
       </c>
       <c r="H43" t="n">
-        <v>436</v>
+        <v>320.5</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
@@ -3111,7 +3081,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-10-20 00:28:03</t>
+          <t>2026-10-20 21:40:56</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3124,21 +3094,21 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>2637慧洋-KY</t>
+          <t>2408南亞科</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>-1.48%100</t>
+          <t>-3.21%422</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>-1.48%</t>
+          <t>-3.21%</t>
         </is>
       </c>
       <c r="H44" t="n">
-        <v>100</v>
+        <v>422</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
@@ -3172,7 +3142,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-10-20 00:28:03</t>
+          <t>2026-10-20 21:40:56</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3185,21 +3155,21 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>2360致茂</t>
+          <t>2637慧洋-KY</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>+0.25%2005</t>
+          <t>-0.9%99.1</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>+0.25%</t>
+          <t>-0.9%</t>
         </is>
       </c>
       <c r="H45" t="n">
-        <v>2005</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
@@ -3233,7 +3203,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-10-20 00:28:04</t>
+          <t>2026-10-20 21:40:57</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3246,21 +3216,21 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>6488環球晶</t>
+          <t>2360致茂</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>-2.22%882</t>
+          <t>-0.25%2000</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>-2.22%</t>
+          <t>-0.25%</t>
         </is>
       </c>
       <c r="H46" t="n">
-        <v>882</v>
+        <v>2000</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
@@ -3294,7 +3264,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-10-20 00:28:04</t>
+          <t>2026-10-20 21:40:57</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3307,21 +3277,21 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>4966譜瑞-KY</t>
+          <t>6488環球晶</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>-2.41%527</t>
+          <t>-4.31%844</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>-2.41%</t>
+          <t>-4.31%</t>
         </is>
       </c>
       <c r="H47" t="n">
-        <v>527</v>
+        <v>844</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
@@ -3355,7 +3325,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-10-20 00:28:04</t>
+          <t>2026-10-20 21:40:57</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3368,21 +3338,21 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>8150南茂</t>
+          <t>4966譜瑞-KY</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>-2.84%102.5</t>
+          <t>-0.57%524</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>-2.84%</t>
+          <t>-0.57%</t>
         </is>
       </c>
       <c r="H48" t="n">
-        <v>102.5</v>
+        <v>524</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
@@ -3416,7 +3386,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-10-20 00:28:04</t>
+          <t>2026-10-20 21:40:57</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3429,21 +3399,21 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>2317鴻海</t>
+          <t>8150南茂</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>-1.84%239.5</t>
+          <t>-3.32%99.1</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>-1.84%</t>
+          <t>-3.32%</t>
         </is>
       </c>
       <c r="H49" t="n">
-        <v>239.5</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
@@ -3477,7 +3447,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-10-20 00:28:04</t>
+          <t>2026-10-20 21:40:57</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3490,21 +3460,21 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>5347世界</t>
+          <t>2317鴻海</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>-2.39%163.5</t>
+          <t>+0.84%241.5</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>-2.39%</t>
+          <t>+0.84%</t>
         </is>
       </c>
       <c r="H50" t="n">
-        <v>163.5</v>
+        <v>241.5</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
@@ -3538,7 +3508,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-10-20 00:28:04</t>
+          <t>2026-10-20 21:40:57</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3551,41 +3521,102 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
+          <t>5347世界</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>-2.14%160</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>-2.14%</t>
+        </is>
+      </c>
+      <c r="H51" t="n">
+        <v>160</v>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>0%1,000</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="K51" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>+0.00%</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>00981A</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>2026-10-20 21:40:57</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00981A/holdings</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>4</v>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
           <t>2481強茂</t>
         </is>
       </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>-0.63%157.5</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>-0.63%</t>
-        </is>
-      </c>
-      <c r="H51" t="n">
-        <v>157.5</v>
-      </c>
-      <c r="I51" t="inlineStr">
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>-2.54%153.5</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>-2.54%</t>
+        </is>
+      </c>
+      <c r="H52" t="n">
+        <v>153.5</v>
+      </c>
+      <c r="I52" t="inlineStr">
         <is>
           <t>0%5,000</t>
         </is>
       </c>
-      <c r="J51" t="inlineStr">
+      <c r="J52" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="K51" t="n">
+      <c r="K52" t="n">
         <v>5000</v>
       </c>
-      <c r="L51" t="inlineStr">
+      <c r="L52" t="inlineStr">
         <is>
           <t>+0.00%</t>
         </is>
       </c>
-      <c r="M51" t="inlineStr">
+      <c r="M52" t="inlineStr">
         <is>
           <t>登入查看</t>
         </is>

--- a/etf_holdings/2026-10-20_00981A_full_holdings.xlsx
+++ b/etf_holdings/2026-10-20_00981A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-20 21:40:53</t>
+          <t>2026-10-20 22:18:26</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-20 21:40:53</t>
+          <t>2026-10-20 22:18:26</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-20 21:40:53</t>
+          <t>2026-10-20 22:18:26</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-20 21:40:53</t>
+          <t>2026-10-20 22:18:26</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-20 21:40:53</t>
+          <t>2026-10-20 22:18:26</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-20 21:40:53</t>
+          <t>2026-10-20 22:18:26</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-20 21:40:53</t>
+          <t>2026-10-20 22:18:26</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-20 21:40:53</t>
+          <t>2026-10-20 22:18:26</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-20 21:40:53</t>
+          <t>2026-10-20 22:18:26</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-20 21:40:53</t>
+          <t>2026-10-20 22:18:26</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-20 21:40:53</t>
+          <t>2026-10-20 22:18:26</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-20 21:40:53</t>
+          <t>2026-10-20 22:18:26</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-20 21:40:53</t>
+          <t>2026-10-20 22:18:26</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-20 21:40:53</t>
+          <t>2026-10-20 22:18:26</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-20 21:40:53</t>
+          <t>2026-10-20 22:18:26</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-10-20 21:40:55</t>
+          <t>2026-10-20 22:18:28</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1469,7 +1469,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-10-20 21:40:55</t>
+          <t>2026-10-20 22:18:28</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1532,7 +1532,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-10-20 21:40:55</t>
+          <t>2026-10-20 22:18:28</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1595,7 +1595,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-10-20 21:40:55</t>
+          <t>2026-10-20 22:18:28</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1658,7 +1658,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-10-20 21:40:55</t>
+          <t>2026-10-20 22:18:28</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-10-20 21:40:55</t>
+          <t>2026-10-20 22:18:28</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1784,7 +1784,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-10-20 21:40:55</t>
+          <t>2026-10-20 22:18:28</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1847,7 +1847,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-10-20 21:40:55</t>
+          <t>2026-10-20 22:18:28</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1910,7 +1910,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-10-20 21:40:55</t>
+          <t>2026-10-20 22:18:28</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1973,7 +1973,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-10-20 21:40:55</t>
+          <t>2026-10-20 22:18:28</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-10-20 21:40:55</t>
+          <t>2026-10-20 22:18:28</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2099,7 +2099,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-10-20 21:40:55</t>
+          <t>2026-10-20 22:18:28</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2162,7 +2162,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-10-20 21:40:55</t>
+          <t>2026-10-20 22:18:28</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2225,7 +2225,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-10-20 21:40:55</t>
+          <t>2026-10-20 22:18:28</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2288,7 +2288,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-10-20 21:40:56</t>
+          <t>2026-10-20 22:18:29</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2349,7 +2349,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-10-20 21:40:56</t>
+          <t>2026-10-20 22:18:29</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2410,7 +2410,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-10-20 21:40:56</t>
+          <t>2026-10-20 22:18:29</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-10-20 21:40:56</t>
+          <t>2026-10-20 22:18:29</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2532,7 +2532,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-10-20 21:40:56</t>
+          <t>2026-10-20 22:18:29</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2593,7 +2593,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-10-20 21:40:56</t>
+          <t>2026-10-20 22:18:29</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2654,7 +2654,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-10-20 21:40:56</t>
+          <t>2026-10-20 22:18:29</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2715,7 +2715,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-10-20 21:40:56</t>
+          <t>2026-10-20 22:18:29</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2776,7 +2776,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-10-20 21:40:56</t>
+          <t>2026-10-20 22:18:29</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2837,7 +2837,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-10-20 21:40:56</t>
+          <t>2026-10-20 22:18:29</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2898,7 +2898,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-10-20 21:40:56</t>
+          <t>2026-10-20 22:18:29</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2959,7 +2959,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-10-20 21:40:56</t>
+          <t>2026-10-20 22:18:29</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -3020,7 +3020,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-10-20 21:40:56</t>
+          <t>2026-10-20 22:18:29</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3081,7 +3081,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-10-20 21:40:56</t>
+          <t>2026-10-20 22:18:29</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3142,7 +3142,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-10-20 21:40:56</t>
+          <t>2026-10-20 22:18:29</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3203,7 +3203,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-10-20 21:40:57</t>
+          <t>2026-10-20 22:18:31</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3264,7 +3264,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-10-20 21:40:57</t>
+          <t>2026-10-20 22:18:31</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3325,7 +3325,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-10-20 21:40:57</t>
+          <t>2026-10-20 22:18:31</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3386,7 +3386,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-10-20 21:40:57</t>
+          <t>2026-10-20 22:18:31</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3447,7 +3447,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-10-20 21:40:57</t>
+          <t>2026-10-20 22:18:31</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3508,7 +3508,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-10-20 21:40:57</t>
+          <t>2026-10-20 22:18:31</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3569,7 +3569,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2026-10-20 21:40:57</t>
+          <t>2026-10-20 22:18:31</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
